--- a/frontend/public/plantilla_docentes_SIGAP.xlsx
+++ b/frontend/public/plantilla_docentes_SIGAP.xlsx
@@ -159,19 +159,19 @@
     <t>Roles</t>
   </si>
   <si>
-    <t>Docente, Director, Consultor, Planeación</t>
-  </si>
-  <si>
-    <t>Puede ingresar uno o varios separados por coma.</t>
+    <t>Docente, Director, Consultor, Planeación, Investigación</t>
+  </si>
+  <si>
+    <t>Puede ingresar uno o varios separados por coma. Un rol que no exista rechaza la fila.</t>
   </si>
   <si>
     <t>Condicional</t>
   </si>
   <si>
-    <t>Ingeniería de Sistemas, Electrónica, Industrial, Financiera...</t>
-  </si>
-  <si>
-    <t>Requerido para Docente y Director. Si es solo Consultor o Planeación use "No aplica".</t>
+    <t>Escriba el nombre del programa (ej. Ingeniería de Sistemas, Ingeniería Electrónica, Ingeniería Industrial…)</t>
+  </si>
+  <si>
+    <t>Obligatorio para Docente, Director e Investigación. Debe existir y no ser ambiguo: "Ingeniería" solo se rechaza. Si es solo Consultor o Planeación use "No aplica". Un Director gestiona el programa indicado y un programa tiene un solo director.</t>
   </si>
 </sst>
 </file>
